--- a/sources/eddy_step8.xlsx
+++ b/sources/eddy_step8.xlsx
@@ -856,6 +856,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
@@ -918,6 +923,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
@@ -978,6 +988,11 @@
       <c r="U8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>89b9a62a-0e17-41f7-9bcd-95c83f81b48a</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -16885,6 +16900,11 @@
           <t>mmmhhmmmhmmm</t>
         </is>
       </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
+        </is>
+      </c>
       <c r="Z189" t="inlineStr">
         <is>
           <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
@@ -16932,6 +16952,11 @@
           <t>mmmhhL</t>
         </is>
       </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
+        </is>
+      </c>
       <c r="Z190" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
@@ -16962,6 +16987,11 @@
       <c r="S191" t="inlineStr">
         <is>
           <t>mmmhhL</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
